--- a/data/merged_panel_wide.xlsx
+++ b/data/merged_panel_wide.xlsx
@@ -502,9 +502,7 @@
       <c r="D2" t="n">
         <v>53.47</v>
       </c>
-      <c r="E2" t="n">
-        <v>10.272</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>-9.575640169934076</v>
       </c>
@@ -517,9 +515,7 @@
       <c r="I2" t="n">
         <v>3.014</v>
       </c>
-      <c r="J2" t="n">
-        <v>47.97756159999999</v>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>24.84412275600621</v>
       </c>
@@ -1867,24 +1863,16 @@
       <c r="D37" t="n">
         <v>57.601</v>
       </c>
-      <c r="E37" t="n">
-        <v>2.351</v>
-      </c>
-      <c r="F37" t="n">
-        <v>-11.69999848202703</v>
-      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
         <v>635.3553275025167</v>
       </c>
-      <c r="H37" t="n">
-        <v>36.458179473877</v>
-      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
         <v>2.708</v>
       </c>
-      <c r="J37" t="n">
-        <v>56.24680049</v>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="n">
         <v>25.20625572159651</v>
       </c>
@@ -1915,9 +1903,7 @@
       <c r="G38" t="n">
         <v>572.7402609009769</v>
       </c>
-      <c r="H38" t="n">
-        <v>36.458179473877</v>
-      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
         <v>2.643</v>
       </c>
@@ -1954,9 +1940,7 @@
       <c r="G39" t="n">
         <v>356.3507800069331</v>
       </c>
-      <c r="H39" t="n">
-        <v>36.458179473877</v>
-      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
         <v>2.499</v>
       </c>
@@ -1993,9 +1977,7 @@
       <c r="G40" t="n">
         <v>347.8706447208779</v>
       </c>
-      <c r="H40" t="n">
-        <v>36.458179473877</v>
-      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
         <v>2.286</v>
       </c>
@@ -2032,9 +2014,7 @@
       <c r="G41" t="n">
         <v>390.8799642976554</v>
       </c>
-      <c r="H41" t="n">
-        <v>36.458179473877</v>
-      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
         <v>2.084</v>
       </c>
@@ -2071,9 +2051,7 @@
       <c r="G42" t="n">
         <v>443.9248608579757</v>
       </c>
-      <c r="H42" t="n">
-        <v>36.458179473877</v>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
         <v>2.067</v>
       </c>
@@ -2110,9 +2088,7 @@
       <c r="G43" t="n">
         <v>487.068624404558</v>
       </c>
-      <c r="H43" t="n">
-        <v>36.458179473877</v>
-      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
         <v>2.06</v>
       </c>
@@ -2149,9 +2125,7 @@
       <c r="G44" t="n">
         <v>505.0358870579657</v>
       </c>
-      <c r="H44" t="n">
-        <v>36.458179473877</v>
-      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
         <v>1.9</v>
       </c>
@@ -2188,9 +2162,7 @@
       <c r="G45" t="n">
         <v>590.2399473334593</v>
       </c>
-      <c r="H45" t="n">
-        <v>36.458179473877</v>
-      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
         <v>1.81</v>
       </c>
@@ -2227,9 +2199,7 @@
       <c r="G46" t="n">
         <v>582.6698861508952</v>
       </c>
-      <c r="H46" t="n">
-        <v>36.458179473877</v>
-      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
         <v>1.534</v>
       </c>
@@ -3232,24 +3202,18 @@
       <c r="D72" t="n">
         <v>11.705</v>
       </c>
-      <c r="E72" t="n">
-        <v>16.577</v>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="n">
         <v>0.8000005801749808</v>
       </c>
       <c r="G72" t="n">
         <v>2445.183327402582</v>
       </c>
-      <c r="H72" t="n">
-        <v>19.9779891967773</v>
-      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
         <v>4.509</v>
       </c>
-      <c r="J72" t="n">
-        <v>9.764662150000001</v>
-      </c>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="n">
         <v>49.4487950045558</v>
       </c>
@@ -3280,9 +3244,7 @@
       <c r="G73" t="n">
         <v>1759.112016482291</v>
       </c>
-      <c r="H73" t="n">
-        <v>19.9779891967773</v>
-      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="n">
         <v>4.366</v>
       </c>
@@ -3319,9 +3281,7 @@
       <c r="G74" t="n">
         <v>1802.693008012888</v>
       </c>
-      <c r="H74" t="n">
-        <v>19.9779891967773</v>
-      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
         <v>4.274</v>
       </c>
@@ -3358,9 +3318,7 @@
       <c r="G75" t="n">
         <v>1831.048009764494</v>
       </c>
-      <c r="H75" t="n">
-        <v>19.9779891967773</v>
-      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
         <v>4.076</v>
       </c>
@@ -3397,9 +3355,7 @@
       <c r="G76" t="n">
         <v>1525.540617602877</v>
       </c>
-      <c r="H76" t="n">
-        <v>19.9779891967773</v>
-      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="n">
         <v>3.914</v>
       </c>
@@ -3436,9 +3392,7 @@
       <c r="G77" t="n">
         <v>1466.948067604152</v>
       </c>
-      <c r="H77" t="n">
-        <v>19.9779891967773</v>
-      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
         <v>3.487</v>
       </c>
@@ -3475,9 +3429,7 @@
       <c r="G78" t="n">
         <v>1616.831987212851</v>
       </c>
-      <c r="H78" t="n">
-        <v>19.9779891967773</v>
-      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="n">
         <v>3.139</v>
       </c>
@@ -3514,9 +3466,7 @@
       <c r="G79" t="n">
         <v>1628.761005615063</v>
       </c>
-      <c r="H79" t="n">
-        <v>19.9779891967773</v>
-      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="n">
         <v>2.886</v>
       </c>
@@ -3553,9 +3503,7 @@
       <c r="G80" t="n">
         <v>1603.366232008358</v>
       </c>
-      <c r="H80" t="n">
-        <v>19.9779891967773</v>
-      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="n">
         <v>2.691</v>
       </c>
@@ -3592,9 +3540,7 @@
       <c r="G81" t="n">
         <v>1596.118222390247</v>
       </c>
-      <c r="H81" t="n">
-        <v>19.9779891967773</v>
-      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="n">
         <v>2.62</v>
       </c>
@@ -3631,9 +3577,7 @@
       <c r="G82" t="n">
         <v>1772.928691227614</v>
       </c>
-      <c r="H82" t="n">
-        <v>19.9779891967773</v>
-      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="n">
         <v>2.59</v>
       </c>
@@ -3670,9 +3614,7 @@
       <c r="G83" t="n">
         <v>1896.300208780129</v>
       </c>
-      <c r="H83" t="n">
-        <v>19.9779891967773</v>
-      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="n">
         <v>2.519</v>
       </c>
@@ -3709,9 +3651,7 @@
       <c r="G84" t="n">
         <v>1937.464114130188</v>
       </c>
-      <c r="H84" t="n">
-        <v>19.9779891967773</v>
-      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="n">
         <v>2.429</v>
       </c>
@@ -3748,9 +3688,7 @@
       <c r="G85" t="n">
         <v>2283.772993461255</v>
       </c>
-      <c r="H85" t="n">
-        <v>19.9779891967773</v>
-      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="n">
         <v>2.451</v>
       </c>
@@ -4597,9 +4535,7 @@
       <c r="D107" t="n">
         <v>22.188</v>
       </c>
-      <c r="E107" t="n">
-        <v>21.089</v>
-      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="n">
         <v>5.667029157158183</v>
       </c>
@@ -4612,9 +4548,7 @@
       <c r="I107" t="n">
         <v>4.512</v>
       </c>
-      <c r="J107" t="n">
-        <v>17.50877268</v>
-      </c>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="n">
         <v>27.12900541907176</v>
       </c>
@@ -5962,24 +5896,18 @@
       <c r="D142" t="n">
         <v>70.318</v>
       </c>
-      <c r="E142" t="n">
-        <v>2.558</v>
-      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
         <v>-14.78878504672898</v>
       </c>
       <c r="G142" t="n">
         <v>1610.980271468683</v>
       </c>
-      <c r="H142" t="n">
-        <v>34.0329704284668</v>
-      </c>
+      <c r="H142" t="inlineStr"/>
       <c r="I142" t="n">
         <v>2.306</v>
       </c>
-      <c r="J142" t="n">
-        <v>68.51926555999999</v>
-      </c>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="n">
         <v>40.13701871674929</v>
       </c>
@@ -7297,9 +7225,7 @@
       <c r="G176" t="n">
         <v>9241.491223137131</v>
       </c>
-      <c r="H176" t="n">
-        <v>84.09585629400109</v>
-      </c>
+      <c r="H176" t="inlineStr"/>
       <c r="I176" t="n">
         <v>1.802</v>
       </c>
@@ -7327,24 +7253,18 @@
       <c r="D177" t="n">
         <v>9.57</v>
       </c>
-      <c r="E177" t="n">
-        <v>24.598</v>
-      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
         <v>13.59492644358396</v>
       </c>
       <c r="G177" t="n">
         <v>2137.942227398768</v>
       </c>
-      <c r="H177" t="n">
-        <v>14.3763198852539</v>
-      </c>
+      <c r="H177" t="inlineStr"/>
       <c r="I177" t="n">
         <v>4.934</v>
       </c>
-      <c r="J177" t="n">
-        <v>7.215971400000001</v>
-      </c>
+      <c r="J177" t="inlineStr"/>
       <c r="K177" t="n">
         <v>46.23788735873178</v>
       </c>
@@ -7375,9 +7295,7 @@
       <c r="G178" t="n">
         <v>2194.439068036567</v>
       </c>
-      <c r="H178" t="n">
-        <v>14.3763198852539</v>
-      </c>
+      <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
         <v>4.568</v>
       </c>
@@ -7414,9 +7332,7 @@
       <c r="G179" t="n">
         <v>1957.485077942519</v>
       </c>
-      <c r="H179" t="n">
-        <v>14.3763198852539</v>
-      </c>
+      <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
         <v>4.099</v>
       </c>
@@ -7453,9 +7369,7 @@
       <c r="G180" t="n">
         <v>1038.109856820673</v>
       </c>
-      <c r="H180" t="n">
-        <v>14.3763198852539</v>
-      </c>
+      <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
         <v>3.674</v>
       </c>
@@ -7492,9 +7406,7 @@
       <c r="G181" t="n">
         <v>1167.762725137951</v>
       </c>
-      <c r="H181" t="n">
-        <v>14.3763198852539</v>
-      </c>
+      <c r="H181" t="inlineStr"/>
       <c r="I181" t="n">
         <v>3.244</v>
       </c>
@@ -7531,9 +7443,7 @@
       <c r="G182" t="n">
         <v>1550.0095955025</v>
       </c>
-      <c r="H182" t="n">
-        <v>14.3763198852539</v>
-      </c>
+      <c r="H182" t="inlineStr"/>
       <c r="I182" t="n">
         <v>2.852</v>
       </c>
@@ -8623,9 +8533,7 @@
       <c r="G210" t="n">
         <v>5049.299316427539</v>
       </c>
-      <c r="H210" t="n">
-        <v>59.131290435791</v>
-      </c>
+      <c r="H210" t="inlineStr"/>
       <c r="I210" t="n">
         <v>1.695</v>
       </c>
@@ -8662,9 +8570,7 @@
       <c r="G211" t="n">
         <v>5190.169590248213</v>
       </c>
-      <c r="H211" t="n">
-        <v>59.131290435791</v>
-      </c>
+      <c r="H211" t="inlineStr"/>
       <c r="I211" t="n">
         <v>1.684</v>
       </c>
@@ -8692,9 +8598,7 @@
       <c r="D212" t="n">
         <v>11.201</v>
       </c>
-      <c r="E212" t="n">
-        <v>32.183</v>
-      </c>
+      <c r="E212" t="inlineStr"/>
       <c r="F212" t="n">
         <v>-0.2759039075919247</v>
       </c>
@@ -8707,9 +8611,7 @@
       <c r="I212" t="n">
         <v>5.544</v>
       </c>
-      <c r="J212" t="n">
-        <v>7.59618217</v>
-      </c>
+      <c r="J212" t="inlineStr"/>
       <c r="K212" t="n">
         <v>33.89085503050924</v>
       </c>
@@ -10057,24 +9959,18 @@
       <c r="D247" t="n">
         <v>17.975</v>
       </c>
-      <c r="E247" t="n">
-        <v>10.553</v>
-      </c>
+      <c r="E247" t="inlineStr"/>
       <c r="F247" t="n">
         <v>26.53316009324914</v>
       </c>
       <c r="G247" t="n">
         <v>789.5263384847376</v>
       </c>
-      <c r="H247" t="n">
-        <v>23.0771808624268</v>
-      </c>
+      <c r="H247" t="inlineStr"/>
       <c r="I247" t="n">
         <v>3.268</v>
       </c>
-      <c r="J247" t="n">
-        <v>16.07809825</v>
-      </c>
+      <c r="J247" t="inlineStr"/>
       <c r="K247" t="n">
         <v>28.09851132150487</v>
       </c>
@@ -10105,9 +10001,7 @@
       <c r="G248" t="n">
         <v>1278.421257456334</v>
       </c>
-      <c r="H248" t="n">
-        <v>23.0771808624268</v>
-      </c>
+      <c r="H248" t="inlineStr"/>
       <c r="I248" t="n">
         <v>3.162</v>
       </c>
@@ -11236,9 +11130,7 @@
       <c r="G277" t="n">
         <v>5561.19166950397</v>
       </c>
-      <c r="H277" t="n">
-        <v>57.1435211987779</v>
-      </c>
+      <c r="H277" t="inlineStr"/>
       <c r="I277" t="n">
         <v>2.308</v>
       </c>
@@ -11275,9 +11167,7 @@
       <c r="G278" t="n">
         <v>4045.373910662337</v>
       </c>
-      <c r="H278" t="n">
-        <v>57.1435211987779</v>
-      </c>
+      <c r="H278" t="inlineStr"/>
       <c r="I278" t="n">
         <v>2.283</v>
       </c>
@@ -11314,9 +11204,7 @@
       <c r="G279" t="n">
         <v>3654.358455348785</v>
       </c>
-      <c r="H279" t="n">
-        <v>57.1435211987779</v>
-      </c>
+      <c r="H279" t="inlineStr"/>
       <c r="I279" t="n">
         <v>2.263</v>
       </c>
@@ -11353,9 +11241,7 @@
       <c r="G280" t="n">
         <v>3477.724898426838</v>
       </c>
-      <c r="H280" t="n">
-        <v>57.1435211987779</v>
-      </c>
+      <c r="H280" t="inlineStr"/>
       <c r="I280" t="n">
         <v>2.239</v>
       </c>
@@ -11380,30 +11266,16 @@
       <c r="C281" t="n">
         <v>2024</v>
       </c>
-      <c r="D281" t="n">
-        <v>22.234</v>
-      </c>
-      <c r="E281" t="n">
-        <v>14.48</v>
-      </c>
-      <c r="F281" t="n">
-        <v>-0.7605844702573137</v>
-      </c>
-      <c r="G281" t="n">
-        <v>3477.724898426838</v>
-      </c>
-      <c r="H281" t="n">
-        <v>57.1435211987779</v>
-      </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr"/>
+      <c r="H281" t="inlineStr"/>
       <c r="I281" t="n">
         <v>2.227</v>
       </c>
-      <c r="J281" t="n">
-        <v>19.0145168</v>
-      </c>
-      <c r="K281" t="n">
-        <v>58.97223837049801</v>
-      </c>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -11422,9 +11294,7 @@
       <c r="D282" t="n">
         <v>22.819</v>
       </c>
-      <c r="E282" t="n">
-        <v>12.96</v>
-      </c>
+      <c r="E282" t="inlineStr"/>
       <c r="F282" t="n">
         <v>3.411812226301151</v>
       </c>
@@ -11437,9 +11307,7 @@
       <c r="I282" t="n">
         <v>4.06</v>
       </c>
-      <c r="J282" t="n">
-        <v>19.8616576</v>
-      </c>
+      <c r="J282" t="inlineStr"/>
       <c r="K282" t="n">
         <v>35.05810954575104</v>
       </c>
@@ -12787,9 +12655,7 @@
       <c r="D317" t="n">
         <v>22.245</v>
       </c>
-      <c r="E317" t="n">
-        <v>17.374</v>
-      </c>
+      <c r="E317" t="inlineStr"/>
       <c r="F317" t="n">
         <v>7.949819436654607</v>
       </c>
@@ -12802,9 +12668,7 @@
       <c r="I317" t="n">
         <v>3.441</v>
       </c>
-      <c r="J317" t="n">
-        <v>18.3801537</v>
-      </c>
+      <c r="J317" t="inlineStr"/>
       <c r="K317" t="n">
         <v>38.42436212578041</v>
       </c>
@@ -14122,9 +13986,7 @@
       <c r="G351" t="n">
         <v>4181.137893012285</v>
       </c>
-      <c r="H351" t="n">
-        <v>49.398738861084</v>
-      </c>
+      <c r="H351" t="inlineStr"/>
       <c r="I351" t="n">
         <v>1.818</v>
       </c>
@@ -14152,9 +14014,7 @@
       <c r="D352" t="n">
         <v>33.931</v>
       </c>
-      <c r="E352" t="n">
-        <v>7.122</v>
-      </c>
+      <c r="E352" t="inlineStr"/>
       <c r="F352" t="n">
         <v>9.266146671493146</v>
       </c>
@@ -14167,9 +14027,7 @@
       <c r="I352" t="n">
         <v>3.107</v>
       </c>
-      <c r="J352" t="n">
-        <v>31.51443417999999</v>
-      </c>
+      <c r="J352" t="inlineStr"/>
       <c r="K352" t="n">
         <v>51.86064229463736</v>
       </c>
@@ -15487,9 +15345,7 @@
       <c r="G386" t="n">
         <v>15892.71572872408</v>
       </c>
-      <c r="H386" t="n">
-        <v>109.999862670898</v>
-      </c>
+      <c r="H386" t="inlineStr"/>
       <c r="I386" t="n">
         <v>1.48</v>
       </c>
